--- a/p_Marker_CATE_EC1.13.11.2_K07104_K00446/primers_dgp_cate2_Supplementary.xlsx
+++ b/p_Marker_CATE_EC1.13.11.2_K07104_K00446/primers_dgp_cate2_Supplementary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipiit-my.sharepoint.com/personal/g_semeraro1_studenti_unipi_it/Documents/UniPi/Tesi/PRIMERS/tesiR/5_1.13.11.2_K07104_catE/primers_cmelk07104/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipiit-my.sharepoint.com/personal/g_semeraro1_studenti_unipi_it/Documents/UniPi/Tesi/THESIS/p_marker_CATE_EC1.13.11.2_K07104_K00446/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="11_AD4D5CB4E552A5DACE1C6445E8DA5B2E5ADEDD88" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80E7176A-318D-4CCF-9535-D803EA1C0696}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="11_AD4D5CB4E552A5DACE1C6445E8DA5B2E5ADEDD88" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D2EEB08-A5AF-4483-89FB-FE660B388D54}"/>
   <bookViews>
-    <workbookView xWindow="9518" yWindow="0" windowWidth="9765" windowHeight="11363" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -554,10 +554,10 @@
       <c r="E6">
         <v>0.49511699999999997</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="1">
         <v>27</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>3</v>
       </c>
       <c r="H6" t="s">
@@ -580,10 +580,10 @@
       <c r="E7">
         <v>0.87957799999999997</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="1">
         <v>9</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>27</v>
       </c>
       <c r="H7" t="s">
@@ -606,10 +606,10 @@
       <c r="E8">
         <v>0.61886600000000003</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="1">
         <v>9</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>27</v>
       </c>
       <c r="H8" t="s">
